--- a/news_daily/2026-08-13.xlsx
+++ b/news_daily/2026-08-13.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1635,174 +1635,198 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Goldman Sachs</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-08-13T21:41:59+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Goldman Sachs Acquires Food Supply Chain Reusables Solutions Provider Tosca</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQOTBIeXRBZjJQNWt3c3J2WFA3UVBQZ3dyQzBxOXVrVlFwdGp2X2dRX1NWZmJPekpEMkttaDl1OEFGZjRHZ080QXZ0YlN3TnV0TXJ3blY3bi1hSEl3bVJsWUgtMG85b1p0ZjNCZEtmM3RpUWJ1blhBOERWN2g3SExEMm9fOGIzSVVmZkJ4SXVmYndYbmlRZE9pbkcxN2FYX2h3S3Nj?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>ESG Today</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>高盛收購食品供應鏈可重複使用解決方案供應商 Tosca</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>14c34de2be8d495bb70a24cdb310fc0f</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>adab42d9ab64d167f705ce64</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>d41507d9f8405288bbf87150</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQOTBIeXRBZjJQNWt3c3J2WFA3UVBQZ3dyQzBxOXVrVlFwdGp2X2dRX1NWZmJPekpEMkttaDl1OEFGZjRHZ080QXZ0YlN3TnV0TXJ3blY3bi1hSEl3bVJsWUgtMG85b1p0ZjNCZEtmM3RpUWJ1blhBOERWN2g3SExEMm9fOGIzSVVmZkJ4SXVmYndYbmlRZE9pbkcxN2FYX2h3S3Nj?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>ESG Today</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr">
-        <is>
-          <t>高盛收購食品供應鏈可重複使用解決方案供應商 Tosca</t>
-        </is>
-      </c>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>adab42d9ab64d167f705ce64</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>d41507d9f8405288bbf87150</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr"/>
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2028,32 +2052,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2093,7 +2117,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2102,7 +2126,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>a5657399869a4a24ba55e0a9f5cc9b73</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>d56adeac4de405d9a50ede9b</t>
@@ -2125,7 +2153,7 @@
       <c r="AN8" s="2" t="inlineStr"/>
       <c r="AO8" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP8" s="2" t="inlineStr"/>
@@ -2159,10 +2187,22 @@
       <c r="BF8" s="2" t="inlineStr"/>
       <c r="BG8" s="2" t="inlineStr"/>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2343,174 +2383,198 @@
       <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Electronic Arts</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-08-13T21:11:06+08:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>EA Sports' College Football 27 predicts the 2026 season, with a Heisman winner, 12-team playoff and champion</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.051</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQQVI2QnRuYzlCaDBtcDhSVkN0d1JrQjhERFV5eXVZTGtHNEw0Y3JzdHJrZGo2Y1JZQ0hMSUoyZkdiYmVseVpDOTQ2cVpDTy1ETXptazdpdV85bTNmeFhzS3hmOVJ1dGxoQ2YzaFNmSzBDQ05wc0ZFR2daeEdyWTFlQnp4TWVXZFBsZ19MeEtqM0EtMm9iUjQtWWlRQk5odVkzcVp4bzdlVktER25JTExtX1Y2M21OYXpudENfRDA5OXF5d19HbkVhY1NGNm1uaHVtbmY1MHRIcWMyb3pyLThXMnlQMnRBSjk3TU9PVnJPZmg0OWtsZVBVMEJBMVRNZ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Sports</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>EA Sports 的大學橄欖球 27 預測 2026 賽季，海斯曼冠軍、12 隊季後賽和冠軍</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>fa2c49eae3144d6e88790d36bcd94b00</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>9b0ad591f9f9de77d339723e</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>819e5d846752b181b46415f1</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>0.051</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQQVI2QnRuYzlCaDBtcDhSVkN0d1JrQjhERFV5eXVZTGtHNEw0Y3JzdHJrZGo2Y1JZQ0hMSUoyZkdiYmVseVpDOTQ2cVpDTy1ETXptazdpdV85bTNmeFhzS3hmOVJ1dGxoQ2YzaFNmSzBDQ05wc0ZFR2daeEdyWTFlQnp4TWVXZFBsZ19MeEtqM0EtMm9iUjQtWWlRQk5odVkzcVp4bzdlVktER25JTExtX1Y2M21OYXpudENfRDA5OXF5d19HbkVhY1NGNm1uaHVtbmY1MHRIcWMyb3pyLThXMnlQMnRBSjk3TU9PVnJPZmg0OWtsZVBVMEJBMVRNZ3c?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Sports</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>EA Sports 的大學橄欖球 27 預測 2026 賽季，海斯曼冠軍、12 隊季後賽和冠軍</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>9b0ad591f9f9de77d339723e</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>819e5d846752b181b46415f1</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr"/>
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr"/>
-      <c r="BK10" s="4" t="inlineStr"/>
-      <c r="BL10" s="4" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2885,174 +2949,198 @@
       <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>WTW</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Willis Towers Watson</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-08-13T20:00:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>WTW research warns of global vulnerabilities from concentrated lithium supply chains as critical mineral demand grows</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>'-0.934</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdllabkRDVW9XSlJlNlo4bU9NRGRXeklDWnlHNXZmQjRia2Z3bnM0eWxGMS10X21xZ3FNd0RyeWVvSFU2VlFGcW03Q2JyMnBscEdtdDlObF9ocWJYZEdkQ25FSWFSZGphdy1EdE16aHdjVFp5ZktIMnhsVWJRUHFzaFpGbk1rOWRKLWdHMHliNFBvZ293SHd3ZHhQUU1uWkk?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>WTW 研究警告稱，隨著關鍵礦產需求的增長，集中鋰供應鏈將導致全球脆弱性</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>b99865f2ef6f4b24874e712703c75103</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>0979e816cfca667f32b67332</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>fe1bcd9ebdaca440faf06f63</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>'-0.934</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdllabkRDVW9XSlJlNlo4bU9NRGRXeklDWnlHNXZmQjRia2Z3bnM0eWxGMS10X21xZ3FNd0RyeWVvSFU2VlFGcW03Q2JyMnBscEdtdDlObF9ocWJYZEdkQ25FSWFSZGphdy1EdE16aHdjVFp5ZktIMnhsVWJRUHFzaFpGbk1rOWRKLWdHMHliNFBvZ293SHd3ZHhQUU1uWkk?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>WTW 研究警告稱，隨著關鍵礦產需求的增長，集中鋰供應鏈將導致全球脆弱性</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>0979e816cfca667f32b67332</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>fe1bcd9ebdaca440faf06f63</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr"/>
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
         <is>
           <t>WTW</t>
         </is>
       </c>
-      <c r="BC13" s="4" t="inlineStr">
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr"/>
-      <c r="BL13" s="4" t="inlineStr"/>
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5087,7 +5175,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Cisco</t>
@@ -5121,17 +5213,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5180,7 +5272,11 @@
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr"/>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>ba5b2249b2d345c8a9ef5c555dbf37e2</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>4b881c4662c5679162f10858</t>
@@ -5203,7 +5299,7 @@
       <c r="AN25" s="2" t="inlineStr"/>
       <c r="AO25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP25" s="2" t="inlineStr"/>
@@ -5237,10 +5333,22 @@
       <c r="BF25" s="2" t="inlineStr"/>
       <c r="BG25" s="2" t="inlineStr"/>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6497,182 +6605,198 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Bio-Techne</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2026-08-13T03:47:42+08:00</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Tech layoffs hit Seattle housing market as pending sales post sharpest drop in the nation</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>'-0.957</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxObmNWMFh3RzhicktLQkNwMldVN2Iwb0YyR2pRbDRGVVZHZVhRekpILVh6VjBYZWxaeEFCUVBaYndYQXVFVGhKbFpXdzhKYkRyaWhkUFRzU2hoWl9SOENreW1weWdRMnVxMVI2V0hieUdXR1FGbjR0VkhFdmM4OGdBdDNEcjdSN0UzaFptU3ItWjR6S0hHVXRFOVNBcnZDLW92ZS1ETFhtSTBuZkJwVnNfNDExX09INHYxRzNjRHNKbkR0MlJyclc1SGUwT1VSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>GeekWire</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>科技公司裁員打擊西雅圖房地產市場，待售房屋銷售創全國最大跌幅</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>dc0f46e3b7aa41cfb2503565b0e46c30</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>38a3be6fac8f91c8beff1fb6</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>c1d3caa3f2896ead70f880fc</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+      <c r="AK33" s="2" t="inlineStr"/>
+      <c r="AL33" s="2" t="inlineStr"/>
+      <c r="AM33" s="2" t="inlineStr"/>
+      <c r="AN33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>'-0.957</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="4" t="inlineStr"/>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr">
+      <c r="AP33" s="2" t="inlineStr"/>
+      <c r="AQ33" s="2" t="inlineStr"/>
+      <c r="AR33" s="2" t="inlineStr"/>
+      <c r="AS33" s="2" t="inlineStr"/>
+      <c r="AT33" s="2" t="inlineStr"/>
+      <c r="AU33" s="2" t="inlineStr"/>
+      <c r="AV33" s="2" t="inlineStr"/>
+      <c r="AW33" s="2" t="inlineStr"/>
+      <c r="AX33" s="2" t="inlineStr"/>
+      <c r="AY33" s="2" t="inlineStr"/>
+      <c r="AZ33" s="2" t="inlineStr"/>
+      <c r="BA33" s="2" t="inlineStr"/>
+      <c r="BB33" s="2" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="BC33" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U33" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxObmNWMFh3RzhicktLQkNwMldVN2Iwb0YyR2pRbDRGVVZHZVhRekpILVh6VjBYZWxaeEFCUVBaYndYQXVFVGhKbFpXdzhKYkRyaWhkUFRzU2hoWl9SOENreW1weWdRMnVxMVI2V0hieUdXR1FGbjR0VkhFdmM4OGdBdDNEcjdSN0UzaFptU3ItWjR6S0hHVXRFOVNBcnZDLW92ZS1ETFhtSTBuZkJwVnNfNDExX09INHYxRzNjRHNKbkR0MlJyclc1SGUwT1VSQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>GeekWire</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr">
-        <is>
-          <t>科技公司裁員打擊西雅圖房地產市場，待售房屋銷售創全國最大跌幅</t>
-        </is>
-      </c>
-      <c r="X33" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y33" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z33" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="inlineStr">
-        <is>
-          <t>38a3be6fac8f91c8beff1fb6</t>
-        </is>
-      </c>
-      <c r="AD33" s="4" t="inlineStr">
-        <is>
-          <t>c1d3caa3f2896ead70f880fc</t>
-        </is>
-      </c>
-      <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="inlineStr"/>
-      <c r="AG33" s="4" t="inlineStr"/>
-      <c r="AH33" s="4" t="inlineStr"/>
-      <c r="AI33" s="4" t="inlineStr"/>
-      <c r="AJ33" s="4" t="inlineStr"/>
-      <c r="AK33" s="4" t="inlineStr"/>
-      <c r="AL33" s="4" t="inlineStr"/>
-      <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="inlineStr"/>
-      <c r="AO33" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP33" s="4" t="inlineStr"/>
-      <c r="AQ33" s="4" t="inlineStr"/>
-      <c r="AR33" s="4" t="inlineStr"/>
-      <c r="AS33" s="4" t="inlineStr"/>
-      <c r="AT33" s="4" t="inlineStr"/>
-      <c r="AU33" s="4" t="inlineStr"/>
-      <c r="AV33" s="4" t="inlineStr"/>
-      <c r="AW33" s="4" t="inlineStr"/>
-      <c r="AX33" s="4" t="inlineStr"/>
-      <c r="AY33" s="4" t="inlineStr"/>
-      <c r="AZ33" s="4" t="inlineStr"/>
-      <c r="BA33" s="4" t="inlineStr"/>
-      <c r="BB33" s="4" t="inlineStr">
+      <c r="BD33" s="2" t="inlineStr">
         <is>
           <t>TECH</t>
         </is>
       </c>
-      <c r="BC33" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD33" s="4" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="BE33" s="4" t="inlineStr">
+      <c r="BE33" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF33" s="4" t="inlineStr">
+      <c r="BF33" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG33" s="4" t="inlineStr"/>
-      <c r="BH33" s="4" t="inlineStr"/>
-      <c r="BI33" s="4" t="inlineStr"/>
-      <c r="BJ33" s="4" t="inlineStr"/>
-      <c r="BK33" s="4" t="inlineStr"/>
-      <c r="BL33" s="4" t="inlineStr"/>
+      <c r="BG33" s="2" t="inlineStr"/>
+      <c r="BH33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -7297,13 +7421,17 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -7356,7 +7484,11 @@
         </is>
       </c>
       <c r="AA37" s="4" t="inlineStr"/>
-      <c r="AB37" s="4" t="inlineStr"/>
+      <c r="AB37" s="4" t="inlineStr">
+        <is>
+          <t>50ce4bcdd790414eb4eb3ce99a79c8d9</t>
+        </is>
+      </c>
       <c r="AC37" s="4" t="inlineStr">
         <is>
           <t>7309de4f9eb47877992f7055</t>
@@ -7377,7 +7509,11 @@
       <c r="AL37" s="4" t="inlineStr"/>
       <c r="AM37" s="4" t="inlineStr"/>
       <c r="AN37" s="4" t="inlineStr"/>
-      <c r="AO37" s="4" t="inlineStr"/>
+      <c r="AO37" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="4" t="inlineStr"/>
       <c r="AQ37" s="4" t="inlineStr"/>
       <c r="AR37" s="4" t="inlineStr"/>
@@ -7423,8 +7559,16 @@
       <c r="BH37" s="4" t="inlineStr"/>
       <c r="BI37" s="4" t="inlineStr"/>
       <c r="BJ37" s="4" t="inlineStr"/>
-      <c r="BK37" s="4" t="inlineStr"/>
-      <c r="BL37" s="4" t="inlineStr"/>
+      <c r="BK37" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7616,7 +7760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8206,1455 +8350,787 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13T21:41:59+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Goldman Sachs Acquires Food Supply Chain Reusables Solutions Provider Tosca</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PSKY</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Paramount Skydance Corporation</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:18:59+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>派拉蒙考慮出售CNN以解決12州反壟斷訴訟</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2609608</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>派拉蒙考慮出售CNN以解決12州反壟斷訴訟</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>57f1885ec3a74b3fb565acb22b6f4b9a</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>62f6c3a64c4e87af310d7469</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>a3ac9ab0fb3928c97bf27f11</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQOTBIeXRBZjJQNWt3c3J2WFA3UVBQZ3dyQzBxOXVrVlFwdGp2X2dRX1NWZmJPekpEMkttaDl1OEFGZjRHZ080QXZ0YlN3TnV0TXJ3blY3bi1hSEl3bVJsWUgtMG85b1p0ZjNCZEtmM3RpUWJ1blhBOERWN2g3SExEMm9fOGIzSVVmZkJ4SXVmYndYbmlRZE9pbkcxN2FYX2h3S3Nj?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>ESG Today</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>高盛收購食品供應鏈可重複使用解決方案供應商 Tosca</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>adab42d9ab64d167f705ce64</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>d41507d9f8405288bbf87150</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr"/>
-      <c r="BG3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="4" t="inlineStr"/>
-      <c r="BI3" s="4" t="inlineStr"/>
-      <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>PSKY</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD3" s="3" t="inlineStr">
+        <is>
+          <t>PSKY</t>
+        </is>
+      </c>
+      <c r="BE3" s="3" t="inlineStr"/>
+      <c r="BF3" s="3" t="inlineStr"/>
+      <c r="BG3" s="3" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13T21:11:06+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>EA Sports' College Football 27 predicts the 2026 season, with a Heisman winner, 12-team playoff and champion</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13T03:17:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Regeneron Pharmaceuticals, Inc. Investors with Substantial Losses Have Opportunity to Lead Regeneron Class Action Lawsuit - Hagens Berman Sobol Shapiro LLP</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.036</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxPSjlucTdPTHlFQUNrQkJfcWlGYmZyQXl3cFdDMGJZOE8xYk0xUTNZUEJiWUlpZ2lKM0ZfQ3lQc1dTbzhJRGVSRVZpS3VsUDEwd3hHcDFEVUJqdGp0b2JjaDBBRk9YQzNYRDIyT2g4bE5vTHpmYi1xdFNDTm9VZktrSU5ZS09FbWZXaXZQZHhXeVdVdjM0MERtTHdfODNyM1YxWkdiMHpBTl9uQzZaWUNDQnhCa3NNaVVFSGdzNE8tSGhlX2ZyT2pNeWFtYi1xbEpoQVRQZmx1MEdJSlB4RzlaYjNnTVk4RmdDM19nbTBOQlZRc04zLWpxM0pmbnVzSEU5cm5WRXJ0ZFZfanR2aTFXc2dHbVpqWjJoUjdsTEpFbm1qeW4zdDhaTkk1YnJyMnhFcGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>再生元製藥公司遭受重大損失的投資者有機會提起再生元集體訴訟 - Hagens Berman Sobol Shapiro LLP</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>260d01db31da451487eb0499cd24b501</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>1702afff3c658de621b5a87d</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>ac9eb76b90e70272f95a2366</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.051</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQQVI2QnRuYzlCaDBtcDhSVkN0d1JrQjhERFV5eXVZTGtHNEw0Y3JzdHJrZGo2Y1JZQ0hMSUoyZkdiYmVseVpDOTQ2cVpDTy1ETXptazdpdV85bTNmeFhzS3hmOVJ1dGxoQ2YzaFNmSzBDQ05wc0ZFR2daeEdyWTFlQnp4TWVXZFBsZ19MeEtqM0EtMm9iUjQtWWlRQk5odVkzcVp4bzdlVktER25JTExtX1Y2M21OYXpudENfRDA5OXF5d19HbkVhY1NGNm1uaHVtbmY1MHRIcWMyb3pyLThXMnlQMnRBSjk3TU9PVnJPZmg0OWtsZVBVMEJBMVRNZ3c?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Sports</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>EA Sports 的大學橄欖球 27 預測 2026 賽季，海斯曼冠軍、12 隊季後賽和冠軍</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>9b0ad591f9f9de77d339723e</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>819e5d846752b181b46415f1</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>WTW</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Willis Towers Watson</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13T20:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>WTW research warns of global vulnerabilities from concentrated lithium supply chains as critical mineral demand grows</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13T03:14:57+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>REGN Stockholders May Be Entitled to Lead the Class Action</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AJBVV95cUxOT29SLTlYSlNJRVpycTNoOFFkdVkxU1M2UE1FNGJrY3lOQVJqZkN4d19xNjdaNFp0bnNMX3FxZTkwRDRVc3AzSkRyb2JDMEJhdG5oTVIzSXZNS3VpV09zakk1R2J0QnZQaEhqLUtLSnJreTlrckpCNTRWSkxPYWNIS1UtQWowZnpiakMtbWY1d0xzQ0l2a002Zk9VOXZkMFZDNlotSEU2VzRDTUVoR1JEeDhZMnVvMWVpOENxVGh5VWtQaHFrVHh3bjduMTZWVkl4QU96Y1RjYlNTeDg3OTIybFA4TU9rb0R5Q3NuOHNQZy1ReGlSZFYyV2JsNTJEcG9LQ3JvS0J2QzR1N2U1Z3IyZURjd1VGNEhvdTNFUE1zUWo2bVJsLWY2SDZVOE15NXY5cjJldnItS0VSRXQtRnhTdjFxbEk3V3Z5S08xYWpJcmJTOVBGUGlRWjVTY1VYOEJBd0l0bA?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>REGN 股東可能有權主導集體訴訟</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>8bf095877e7847e48c4549b04911ec17</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>599666302068ea7e9e2e1608</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>942c6ebe4330f2a7980d9172</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>'-0.934</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdllabkRDVW9XSlJlNlo4bU9NRGRXeklDWnlHNXZmQjRia2Z3bnM0eWxGMS10X21xZ3FNd0RyeWVvSFU2VlFGcW03Q2JyMnBscEdtdDlObF9ocWJYZEdkQ25FSWFSZGphdy1EdE16aHdjVFp5ZktIMnhsVWJRUHFzaFpGbk1rOWRKLWdHMHliNFBvZ293SHd3ZHhQUU1uWkk?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>WTW 研究警告稱，隨著關鍵礦產需求的增長，集中鋰供應鏈將導致全球脆弱性</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>0979e816cfca667f32b67332</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>fe1bcd9ebdaca440faf06f63</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>WTW</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Paramount Skydance Corporation</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13T09:18:59+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>派拉蒙考慮出售CNN以解決12州反壟斷訴訟</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:15:41+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Uber Freight reportedly investigating after hacking group claims data breach</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2609608</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>派拉蒙考慮出售CNN以解決12州反壟斷訴訟</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>57f1885ec3a74b3fb565acb22b6f4b9a</t>
-        </is>
-      </c>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>62f6c3a64c4e87af310d7469</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>a3ac9ab0fb3928c97bf27f11</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.925</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPa1V0VWQ0dGdCX3ZjNDdwYzdWdWF3YUNvWXoxU0Vrc3lVbEdlR19CMDVJWDhlUHpESUoyOUZYUnpfWlF3YS1PZm1Dd2FwMzMyMWtJOHZxMXNmOVpGOXV2N19lT0JJQjNrX0Nrb2FFbVVyclp1OUxlQXI1VUpvVEQ2MXppd3FKSUpSZ2EwTzRfNG4tTWJCVmV6SXN0X1BBVUplS2pGVVRjMmlxS3NKRUhybQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>據報道，Uber Freight 在駭客組織聲稱資料外洩後正在進行調查</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>50ce4bcdd790414eb4eb3ce99a79c8d9</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>7309de4f9eb47877992f7055</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>dd7f2946f86b0678ab55f27b</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-      <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr"/>
-      <c r="BG6" s="3" t="inlineStr"/>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Bio-Techne</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13T03:47:42+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Tech layoffs hit Seattle housing market as pending sales post sharpest drop in the nation</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>'-0.957</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxObmNWMFh3RzhicktLQkNwMldVN2Iwb0YyR2pRbDRGVVZHZVhRekpILVh6VjBYZWxaeEFCUVBaYndYQXVFVGhKbFpXdzhKYkRyaWhkUFRzU2hoWl9SOENreW1weWdRMnVxMVI2V0hieUdXR1FGbjR0VkhFdmM4OGdBdDNEcjdSN0UzaFptU3ItWjR6S0hHVXRFOVNBcnZDLW92ZS1ETFhtSTBuZkJwVnNfNDExX09INHYxRzNjRHNKbkR0MlJyclc1SGUwT1VSQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>GeekWire</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>科技公司裁員打擊西雅圖房地產市場，待售房屋銷售創全國最大跌幅</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>38a3be6fac8f91c8beff1fb6</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>c1d3caa3f2896ead70f880fc</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="4" t="inlineStr"/>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr"/>
-      <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13T03:17:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Regeneron Pharmaceuticals, Inc. Investors with Substantial Losses Have Opportunity to Lead Regeneron Class Action Lawsuit - Hagens Berman Sobol Shapiro LLP</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>'-0.036</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxPSjlucTdPTHlFQUNrQkJfcWlGYmZyQXl3cFdDMGJZOE8xYk0xUTNZUEJiWUlpZ2lKM0ZfQ3lQc1dTbzhJRGVSRVZpS3VsUDEwd3hHcDFEVUJqdGp0b2JjaDBBRk9YQzNYRDIyT2g4bE5vTHpmYi1xdFNDTm9VZktrSU5ZS09FbWZXaXZQZHhXeVdVdjM0MERtTHdfODNyM1YxWkdiMHpBTl9uQzZaWUNDQnhCa3NNaVVFSGdzNE8tSGhlX2ZyT2pNeWFtYi1xbEpoQVRQZmx1MEdJSlB4RzlaYjNnTVk4RmdDM19nbTBOQlZRc04zLWpxM0pmbnVzSEU5cm5WRXJ0ZFZfanR2aTFXc2dHbVpqWjJoUjdsTEpFbm1qeW4zdDhaTkk1YnJyMnhFcGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>再生元製藥公司遭受重大損失的投資者有機會提起再生元集體訴訟 - Hagens Berman Sobol Shapiro LLP</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>260d01db31da451487eb0499cd24b501</t>
-        </is>
-      </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>1702afff3c658de621b5a87d</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>ac9eb76b90e70272f95a2366</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13T03:14:57+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>REGN Stockholders May Be Entitled to Lead the Class Action</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5AJBVV95cUxOT29SLTlYSlNJRVpycTNoOFFkdVkxU1M2UE1FNGJrY3lOQVJqZkN4d19xNjdaNFp0bnNMX3FxZTkwRDRVc3AzSkRyb2JDMEJhdG5oTVIzSXZNS3VpV09zakk1R2J0QnZQaEhqLUtLSnJreTlrckpCNTRWSkxPYWNIS1UtQWowZnpiakMtbWY1d0xzQ0l2a002Zk9VOXZkMFZDNlotSEU2VzRDTUVoR1JEeDhZMnVvMWVpOENxVGh5VWtQaHFrVHh3bjduMTZWVkl4QU96Y1RjYlNTeDg3OTIybFA4TU9rb0R5Q3NuOHNQZy1ReGlSZFYyV2JsNTJEcG9LQ3JvS0J2QzR1N2U1Z3IyZURjd1VGNEhvdTNFUE1zUWo2bVJsLWY2SDZVOE15NXY5cjJldnItS0VSRXQtRnhTdjFxbEk3V3Z5S08xYWpJcmJTOVBGUGlRWjVTY1VYOEJBd0l0bA?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>REGN 股東可能有權主導集體訴訟</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>8bf095877e7847e48c4549b04911ec17</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>599666302068ea7e9e2e1608</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>942c6ebe4330f2a7980d9172</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13T01:15:41+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Uber Freight reportedly investigating after hacking group claims data breach</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.925</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPa1V0VWQ0dGdCX3ZjNDdwYzdWdWF3YUNvWXoxU0Vrc3lVbEdlR19CMDVJWDhlUHpESUoyOUZYUnpfWlF3YS1PZm1Dd2FwMzMyMWtJOHZxMXNmOVpGOXV2N19lT0JJQjNrX0Nrb2FFbVVyclp1OUxlQXI1VUpvVEQ2MXppd3FKSUpSZ2EwTzRfNG4tTWJCVmV6SXN0X1BBVUplS2pGVVRjMmlxS3NKRUhybQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>TechCrunch</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>據報道，Uber Freight 在駭客組織聲稱資料外洩後正在進行調查</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>7309de4f9eb47877992f7055</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>dd7f2946f86b0678ab55f27b</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr"/>
-      <c r="BK10" s="4" t="inlineStr"/>
-      <c r="BL10" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL10"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9665,7 +9141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL4"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10056,518 +9532,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13T21:35:43+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Cerebras股價重挫，喜憂參半的季度業績令其AI增長敘事面臨考驗</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>股價下跌</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-CSCO/news/</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Cerebras股價重挫，喜憂參半的季度業績令其AI增長敘事面臨考驗</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>重挫</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>d56adeac4de405d9a50ede9b</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>b27ff1a1eb8711abe3d8c419</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr"/>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13T09:41:06+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>營收利潤雙超預期，AI訂單爆了！思科為何盤後重挫？</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>股價下跌</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/p/6040935</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>營收利潤雙超預期，AI訂單爆了！思科為何盤後重挫？</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>重挫</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>4b881c4662c5679162f10858</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2b658db25202461f594b7151</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr"/>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Bio-Techne</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13T03:47:42+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Tech layoffs hit Seattle housing market as pending sales post sharpest drop in the nation</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.957</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxObmNWMFh3RzhicktLQkNwMldVN2Iwb0YyR2pRbDRGVVZHZVhRekpILVh6VjBYZWxaeEFCUVBaYndYQXVFVGhKbFpXdzhKYkRyaWhkUFRzU2hoWl9SOENreW1weWdRMnVxMVI2V0hieUdXR1FGbjR0VkhFdmM4OGdBdDNEcjdSN0UzaFptU3ItWjR6S0hHVXRFOVNBcnZDLW92ZS1ETFhtSTBuZkJwVnNfNDExX09INHYxRzNjRHNKbkR0MlJyclc1SGUwT1VSQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>GeekWire</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>科技公司裁員打擊西雅圖房地產市場，待售房屋銷售創全國最大跌幅</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>38a3be6fac8f91c8beff1fb6</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>c1d3caa3f2896ead70f880fc</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL4"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-13.xlsx
+++ b/news_daily/2026-08-13.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>62e1f430507f466fa885106cce506f09</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>67a013153872f07ca859e745</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1027,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2238,28 +2262,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2303,7 +2331,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2312,7 +2340,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>285d35ea862c4beab981953dbbd311ed</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>59a0ec0d071a9bd7aef4aeb1</t>
@@ -2333,7 +2365,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2377,10 +2413,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2804,28 +2852,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2869,7 +2921,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2878,7 +2930,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>7c9c783fc7a6412d901af701bd45025a</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>db460c654a48cd0e6b520946</t>
@@ -2899,7 +2955,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2943,10 +3003,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,13 +3263,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3250,7 +3326,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>06456869c11740359cba406065c6b584</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>af0d0ef86e6abdf3c7fa8a90</t>
@@ -3271,7 +3351,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3317,8 +3401,16 @@
       <c r="BH14" s="2" t="inlineStr"/>
       <c r="BI14" s="2" t="inlineStr"/>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3354,28 +3446,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3419,7 +3515,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3428,7 +3524,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>f852be2e34db48248f5ac3e012718c36</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>9f0990a028c0dfb6e7a47f41</t>
@@ -3449,7 +3549,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3493,10 +3597,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3943,13 +4059,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4002,7 +4122,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>78e22d168e044d50ae19725d227e3332</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>c2bb6bca60e2a980c36017e1</t>
@@ -4023,7 +4147,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4061,8 +4189,16 @@
       <c r="BH18" s="2" t="inlineStr"/>
       <c r="BI18" s="2" t="inlineStr"/>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4113,13 +4249,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4172,7 +4312,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>e925429496524a2587ef1da7d0e63e92</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>099a620b18eb9b6f8c8fe528</t>
@@ -4193,7 +4337,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4239,8 +4387,16 @@
       <c r="BH19" s="2" t="inlineStr"/>
       <c r="BI19" s="2" t="inlineStr"/>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4276,28 +4432,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4341,7 +4501,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4350,7 +4510,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>8dcbb560c4de42b0bee459d21db0a430</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>ac670dc4597acff942a50c00</t>
@@ -4371,7 +4535,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4415,10 +4583,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4454,28 +4634,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4519,7 +4703,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4528,7 +4712,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>2cf74bd16c944e80b521c124a1236ed8</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>d990b1864e52af90226f339a</t>
@@ -4549,7 +4737,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4593,10 +4785,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5020,28 +5224,32 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5085,7 +5293,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -5094,7 +5302,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0303092143cc42f4bf55d784e2801ce3</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>ab415653945cb653b1846f56</t>
@@ -5115,7 +5327,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -5159,10 +5375,22 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
-      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ24" s="2" t="inlineStr"/>
-      <c r="BK24" s="2" t="inlineStr"/>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5570,28 +5798,32 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5635,7 +5867,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -5644,7 +5876,11 @@
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>a2b84054bae04d6aa93a9959301b6bcc</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>a1caf3c38eacc757b26867a4</t>
@@ -5665,7 +5901,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5709,10 +5949,22 @@
         </is>
       </c>
       <c r="BH27" s="2" t="inlineStr"/>
-      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ27" s="2" t="inlineStr"/>
-      <c r="BK27" s="2" t="inlineStr"/>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5748,28 +6000,32 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5813,7 +6069,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -5822,7 +6078,11 @@
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>50899f766a774009b7bddab1577f35f8</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>e9622acc2d99b2ef3c94da58</t>
@@ -5843,7 +6103,11 @@
       <c r="AL28" s="2" t="inlineStr"/>
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -5887,10 +6151,22 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
-      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5926,28 +6202,32 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5991,7 +6271,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -6000,7 +6280,11 @@
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>6c7209b6921a4146a9157e9ab6bc0869</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>176a1a7fc6be154700e205e4</t>
@@ -6021,7 +6305,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -6057,10 +6345,22 @@
         </is>
       </c>
       <c r="BH29" s="2" t="inlineStr"/>
-      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6096,28 +6396,32 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6161,7 +6465,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -6170,7 +6474,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>80d749c738194bb89c71ac774dfb91a8</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>23e11f2dc78a44b92b6898e9</t>
@@ -6191,7 +6499,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -6235,10 +6547,22 @@
         </is>
       </c>
       <c r="BH30" s="2" t="inlineStr"/>
-      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6274,28 +6598,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6339,7 +6667,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6348,7 +6676,11 @@
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>e5211bf64be149a6ae198d26f9f97f42</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>295b00ec23325bb03255c43f</t>
@@ -6369,7 +6701,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6405,10 +6741,22 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7228,28 +7576,32 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -7293,7 +7645,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -7302,7 +7654,11 @@
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr"/>
-      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>6f6147a290c74798b88e023be682f9fb</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>202924385c6ecb4bf4d09c46</t>
@@ -7323,7 +7679,11 @@
       <c r="AL36" s="2" t="inlineStr"/>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
-      <c r="AO36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="2" t="inlineStr"/>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
@@ -7367,10 +7727,22 @@
         </is>
       </c>
       <c r="BH36" s="2" t="inlineStr"/>
-      <c r="BI36" s="2" t="inlineStr"/>
+      <c r="BI36" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ36" s="2" t="inlineStr"/>
-      <c r="BK36" s="2" t="inlineStr"/>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -7604,28 +7976,32 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -7669,7 +8045,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -7678,7 +8054,11 @@
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr"/>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>63de3ea5312f4869af6d98216d084eb0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>e8d819e42af81e678840a6ba</t>
@@ -7699,7 +8079,11 @@
       <c r="AL38" s="2" t="inlineStr"/>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="2" t="inlineStr"/>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
@@ -7743,10 +8127,22 @@
         </is>
       </c>
       <c r="BH38" s="2" t="inlineStr"/>
-      <c r="BI38" s="2" t="inlineStr"/>
+      <c r="BI38" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ38" s="2" t="inlineStr"/>
-      <c r="BK38" s="2" t="inlineStr"/>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL38"/>
